--- a/ksoft_old/docs/records/Stock_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Records.xlsx
@@ -2024,13 +2024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69C1BB9-FF84-4CAD-B9E7-01AFF9E1E693}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BDDF9F-BC11-4EE9-8BD1-21E078853292}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C72363-25C9-4E18-B4D8-56D002A31D28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01D86510-57DD-45CC-A7BD-407467A01A82}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57995813-A023-48A7-AA74-280C3D4DD367}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C27E1D5A-DDAB-46A4-B5AB-7F0F009FD852}"/>
 </file>
--- a/ksoft_old/docs/records/Stock_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Records.xlsx
@@ -2024,13 +2024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BDDF9F-BC11-4EE9-8BD1-21E078853292}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F120C129-D218-4FEF-B8EF-48B7D93DC390}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01D86510-57DD-45CC-A7BD-407467A01A82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F13453D-56A6-479C-83B9-D798779AB8EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C27E1D5A-DDAB-46A4-B5AB-7F0F009FD852}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD15682A-7732-410E-B811-BEDE6F1A5579}"/>
 </file>
--- a/ksoft_old/docs/records/Stock_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Records.xlsx
@@ -2024,13 +2024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F120C129-D218-4FEF-B8EF-48B7D93DC390}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A69C1BB9-FF84-4CAD-B9E7-01AFF9E1E693}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F13453D-56A6-479C-83B9-D798779AB8EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4C72363-25C9-4E18-B4D8-56D002A31D28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD15682A-7732-410E-B811-BEDE6F1A5579}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57995813-A023-48A7-AA74-280C3D4DD367}"/>
 </file>